--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192009</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192010</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1023,6 +1038,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192011</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192012</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1257,6 +1282,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192003</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192004</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1486,6 +1521,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192006</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1603,6 +1643,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192007</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1720,8 +1765,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192008</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135192009</v>
       </c>
       <c r="B2" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135192010</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135192011</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>135192012</v>
       </c>
       <c r="B5" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135192003</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1293,7 +1293,7 @@
         <v>135192004</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>135192006</v>
       </c>
       <c r="B8" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>135192007</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135192008</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,7 +680,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135192004</v>
+        <v>135192009</v>
       </c>
       <c r="B2" t="n">
         <v>57980</v>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456823</v>
+        <v>457107</v>
       </c>
       <c r="R2" t="n">
-        <v>6922820</v>
+        <v>6923147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Möjligt gammal/påbörjat bohål, ca 4,5 m upp i granhögstubbe</t>
+          <t>färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,13 +796,992 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135192009</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135192010</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>457136</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6923187</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135192011</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>457112</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6923219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192011</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135192012</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>457137</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6923325</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192012</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135192003</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>456822</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6922807</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135192004</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>456823</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6922820</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Möjligt gammal/påbörjat bohål, ca 4,5 m upp i granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135192004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135192006</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>456831</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6922844</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192006</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135192007</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>456835</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6922851</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192007</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135192008</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>456855</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6922855</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192008</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135192009</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135192010</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135192011</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>135192012</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135192003</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>135192006</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>135192007</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135192008</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135192004</v>
+        <v>135192009</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456823</v>
+        <v>457107</v>
       </c>
       <c r="R2" t="n">
-        <v>6922820</v>
+        <v>6923147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Möjligt gammal/påbörjat bohål, ca 4,5 m upp i granhögstubbe</t>
+          <t>färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,13 +796,992 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135192009</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135192010</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>457136</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6923187</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135192011</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>457112</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6923219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192011</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135192012</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>457137</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6923325</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192012</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135192003</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>456822</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6922807</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135192004</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>456823</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6922820</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Möjligt gammal/påbörjat bohål, ca 4,5 m upp i granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135192004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135192006</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>456831</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6922844</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192006</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135192007</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>456835</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6922851</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192007</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135192008</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>456855</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6922855</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192008</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135192009</v>
       </c>
       <c r="B2" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135192010</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135192011</v>
       </c>
       <c r="B4" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>135192012</v>
       </c>
       <c r="B5" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135192003</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>135192006</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>135192007</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135192008</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135192009</v>
       </c>
       <c r="B2" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135192010</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135192011</v>
       </c>
       <c r="B4" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>135192012</v>
       </c>
       <c r="B5" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135192003</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>135192006</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>135192007</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135192008</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135192009</v>
       </c>
       <c r="B2" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135192010</v>
       </c>
       <c r="B3" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135192011</v>
       </c>
       <c r="B4" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>135192012</v>
       </c>
       <c r="B5" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135192003</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>135192006</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>135192007</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135192008</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135192009</v>
       </c>
       <c r="B2" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>135192010</v>
       </c>
       <c r="B3" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>135192011</v>
       </c>
       <c r="B4" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>135192012</v>
       </c>
       <c r="B5" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>135192003</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>135192006</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
         <v>135192007</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>135192008</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 28966-2026 artfynd.xlsx
+++ b/artfynd/A 28966-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135192004</v>
+        <v>135192009</v>
       </c>
       <c r="B2" t="n">
-        <v>57980</v>
+        <v>58006</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -711,7 +711,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +720,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>456823</v>
+        <v>457107</v>
       </c>
       <c r="R2" t="n">
-        <v>6922820</v>
+        <v>6923147</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Möjligt gammal/påbörjat bohål, ca 4,5 m upp i granhögstubbe</t>
+          <t>färska och äldre ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,13 +796,992 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135192009</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135192010</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>457136</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6923187</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192010</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135192011</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>457112</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6923219</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192011</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135192012</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>457137</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6923325</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192012</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135192003</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>456822</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6922807</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135192004</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>456823</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6922820</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Möjligt gammal/påbörjat bohål, ca 4,5 m upp i granhögstubbe</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135192004</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135192006</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>456831</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6922844</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192006</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135192007</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>456835</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6922851</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192007</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135192008</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58006</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Johankölen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>456855</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6922855</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135192008</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
